--- a/sheet/Hustle_Math.xlsx
+++ b/sheet/Hustle_Math.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1) Go to File → Make a copy (this file is view-only for everyone else).  2) Type ONLY in YELLOW cells.  3) GREEN cells are formulas — don't type over them.  4) Replace every row marked EXAMPLE with your own numbers, or clear it.</t>
+          <t>1) Save a copy before you type in it.  2) Type ONLY in YELLOW cells.  3) GREEN cells are formulas — don't type over them.  4) Replace every row marked EXAMPLE with your own numbers, or clear it.</t>
         </is>
       </c>
       <c r="D6" s="1" t="n"/>
